--- a/results/Supplementary_Table_7_PhyloGLM_hits.xlsx
+++ b/results/Supplementary_Table_7_PhyloGLM_hits.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,67 +417,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>HOG</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Orb-weaving coefficient estimate</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Orb-weaving coefficient standard error</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Orb-weaving coefficient z-value</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Orb-weaving coefficient p-value</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>p_adj_bonferroni</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>U. diversus gene ID</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>U. diversus GO terms</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>U. diversus gene description</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>P. tepidariorum best BLAST hit LOC</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>P. tepidariorum best BLAST hit description</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>U. diversus best BLAST hit LOC</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>U. diversus best BLAST hit description</t>
         </is>
@@ -3500,12 +3488,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>129224446</t>
+          <t>129224445</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>GO:0005886 [Name: plasma membrane]; GO:0005243 [Name: gap junction channel activity]; GO:0005921 [Name: gap junction]; GO:0007602 [Name: phototransduction]</t>
+          <t>GO:0005921 [Name: gap junction]; GO:0007602 [Name: phototransduction]; GO:0005886 [Name: plasma membrane]; GO:0005243 [Name: gap junction channel activity]</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4046,7 +4034,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>129224663</t>
+          <t>129225116</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4056,7 +4044,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129224663</t>
+          <t>uncharacterized LOC129225116</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -13730,17 +13718,17 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>129224060</t>
+          <t>129224059</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>GO:0030246 [Name: carbohydrate binding]; GO:0005975 [Name: carbohydrate metabolic process]; GO:0016853 [Name: isomerase activity]</t>
+          <t>GO:0016853 [Name: isomerase activity]; GO:0030246 [Name: carbohydrate binding]; GO:0005975 [Name: carbohydrate metabolic process]</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129224060</t>
+          <t>uncharacterized LOC129224059</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -17097,9 +17085,21 @@
       <c r="F303" t="n">
         <v>0.0317015591786932</v>
       </c>
-      <c r="G303" t="inlineStr"/>
-      <c r="H303" t="inlineStr"/>
-      <c r="I303" t="inlineStr"/>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>129234480</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>GO:0005615 [Name: extracellular space]; GO:0005515 [Name: protein binding]; GO:0031012 [Name: extracellular matrix]</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>leucine rich repeat containing protein 20 sclp</t>
+        </is>
+      </c>
       <c r="J303" t="inlineStr">
         <is>
           <t>LOC107436710</t>
@@ -18032,12 +18032,12 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>129218840</t>
+          <t>129225077</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>GO:0000723 [Name: telomere maintenance]; GO:0005634 [Name: nucleus]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -18317,17 +18317,17 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>129218287</t>
+          <t>129216537</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>GO:0006369 [Name: termination of RNA polymerase II transcription]; GO:0005849 [Name: mRNA cleavage factor complex]; GO:0005737 [Name: cytoplasm]; GO:0000993 [Name: RNA polymerase II core binding]; GO:0003729 [Name: mRNA binding]</t>
+          <t>GO:0006369 [Name: termination of RNA polymerase II transcription]; GO:0000993 [Name: RNA polymerase II core binding]; GO:0005849 [Name: mRNA cleavage factor complex]; GO:0005737 [Name: cytoplasm]; GO:0003729 [Name: mRNA binding]</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129218287</t>
+          <t>uncharacterized LOC129216537</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
@@ -18533,17 +18533,17 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>129222745</t>
+          <t>129222744</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>GO:0030036 [Name: actin cytoskeleton organization]; GO:0005886 [Name: plasma membrane]</t>
+          <t>GO:0005886 [Name: plasma membrane]; GO:0030036 [Name: actin cytoskeleton organization]</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129222745</t>
+          <t>uncharacterized LOC129222744</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
